--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-31.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-31.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +623,8 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -692,6 +704,8 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -771,6 +785,8 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -850,6 +866,8 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -929,6 +947,8 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1008,6 +1028,8 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1087,6 +1109,8 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1166,6 +1190,8 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1245,6 +1271,8 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1324,6 +1352,8 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1403,6 +1433,8 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1412,37 +1444,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rapid Bucharest x Universitatea Craiova</t>
+          <t>Burgos CF x Real Sociedad B</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Real Sociedad B</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1451,37 +1483,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3.57</v>
+        <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>9.65</v>
+      </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="W13" t="n">
+        <v>9.65</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1491,37 +1533,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ROMANIA 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rapid Bucharest x Universitatea Craiova</t>
+          <t>Burgos x Sociedad B</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Universitatea Craiova</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1530,20 +1572,20 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5.71</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1558,9 +1600,17 @@
           <t>⏳ PENDENTE</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>9.65</v>
+      </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1570,37 +1620,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Aston Villa x Arsenal</t>
+          <t>Rapid Bucharest x Universitatea Craiova</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Rapid Bucharest</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1609,20 +1659,20 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>16.13</v>
+        <v>3.57</v>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1640,6 +1690,8 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1649,37 +1701,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARGENTINA 2</t>
+          <t>ROMANIA 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Los Andes x Acassuso</t>
+          <t>Rapid Bucharest x Universitatea Craiova</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Rapid Bucharest</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Universitatea Craiova</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Over 4.5 FT</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1691,7 +1743,7 @@
         <v>18.5</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>5.71</v>
@@ -1701,7 +1753,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1719,6 +1771,8 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1728,37 +1782,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>ENGLAND 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Puerto Cabello x Academia Anzoategui FC</t>
+          <t>Aston Villa x Arsenal</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Academia Anzoategui FC</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1767,20 +1821,20 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="L17" t="n">
-        <v>22.22</v>
+        <v>16.13</v>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1798,6 +1852,8 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1807,29 +1863,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VENEZUELA 1</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Puerto Cabello x Anzoategui FC</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+          <t>Los Andes x Acassuso</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Acassuso</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Over 4.5 FT</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1838,43 +1902,286 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="L18" t="n">
-        <v>8.699999999999999</v>
+        <v>5.71</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fortaleza EC x Operario PR</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fortaleza EC</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Operario PR</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>20</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="M19" t="n">
+        <v>200</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VENEZUELA 1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Puerto Cabello x Academia Anzoategui FC</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Puerto Cabello</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Academia Anzoategui FC</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Match Odds (Draw)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="M20" t="n">
+        <v>100</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>3x0</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VENEZUELA 1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Puerto Cabello x Anzoategui FC</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Match Odds (Away)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M21" t="n">
+        <v>100</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>3x0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="P18" t="n">
+      <c r="P21" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
         <v>8.4</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T21" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>LIQUIDADO</t>
         </is>
       </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-31.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-31.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -929,12 +929,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0x4</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1915,12 +1915,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1996,12 +1996,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-31.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-31.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -929,12 +929,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>0x4</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>RED</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1915,12 +1915,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1996,12 +1996,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-31.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-31.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1585,19 +1585,19 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1996,19 +1996,19 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S19" t="n">
